--- a/tests/fixtures/xlsx-pivots/recipes/pivot-source.xlsx
+++ b/tests/fixtures/xlsx-pivots/recipes/pivot-source.xlsx
@@ -83,12 +83,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
